--- a/Compare/Fourth Pass/Taiwo_Coding.xlsx
+++ b/Compare/Fourth Pass/Taiwo_Coding.xlsx
@@ -3049,7 +3049,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>general_pii</t>
+          <t>unspecified</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>polite</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>prospective</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>conversation</t>
+          <t>prospective</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>backend_db</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>conversation</t>
+          <t>prospective</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
